--- a/data/trans_orig/P68-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P68-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62882</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96354</t>
+          <t>94876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43072</t>
+          <t>42974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92816</t>
+          <t>94512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131604</t>
+          <t>134657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282795</t>
+          <t>284273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>316267</t>
+          <t>314498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111575</t>
+          <t>111673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131046</t>
+          <t>131636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>402192</t>
+          <t>399139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440980</t>
+          <t>439284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126865</t>
+          <t>125011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168382</t>
+          <t>169085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41270</t>
+          <t>40992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69152</t>
+          <t>67529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>173133</t>
+          <t>172114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>224370</t>
+          <t>223680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383539</t>
+          <t>382836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425056</t>
+          <t>426910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196950</t>
+          <t>198573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224832</t>
+          <t>225110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>593653</t>
+          <t>594343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>644890</t>
+          <t>645909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91471</t>
+          <t>91825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130743</t>
+          <t>130773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59327</t>
+          <t>57945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136368</t>
+          <t>135314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180696</t>
+          <t>179633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276677</t>
+          <t>276647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315949</t>
+          <t>315595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153786</t>
+          <t>155168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178679</t>
+          <t>178137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439836</t>
+          <t>440899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>484164</t>
+          <t>485218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117713</t>
+          <t>118109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158000</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73476</t>
+          <t>71770</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105527</t>
+          <t>106432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198045</t>
+          <t>198277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>249947</t>
+          <t>252820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>396945</t>
+          <t>394327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>437232</t>
+          <t>436836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282075</t>
+          <t>281170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314126</t>
+          <t>315832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>692600</t>
+          <t>689727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>744502</t>
+          <t>744270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>432161</t>
+          <t>434510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>506905</t>
+          <t>510003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195809</t>
+          <t>196389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249326</t>
+          <t>247541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>644460</t>
+          <t>646055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>737682</t>
+          <t>740870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1386530</t>
+          <t>1383432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1461274</t>
+          <t>1458925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>772138</t>
+          <t>773923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>825655</t>
+          <t>825075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2177217</t>
+          <t>2174029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2270439</t>
+          <t>2268844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62742</t>
+          <t>64228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92313</t>
+          <t>93602</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25266</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>49076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94817</t>
+          <t>94778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132593</t>
+          <t>131923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>176624</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206195</t>
+          <t>204709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114220</t>
+          <t>112199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136009</t>
+          <t>135235</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>298289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335395</t>
+          <t>335434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>77025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114205</t>
+          <t>111032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>50013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>78594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137764</t>
+          <t>135994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180692</t>
+          <t>179462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294486</t>
+          <t>297659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330588</t>
+          <t>331666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190634</t>
+          <t>193002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220322</t>
+          <t>221583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499595</t>
+          <t>500825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>542523</t>
+          <t>544293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>65886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97622</t>
+          <t>97227</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>40318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110565</t>
+          <t>111793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153766</t>
+          <t>154599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>224767</t>
+          <t>225162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258386</t>
+          <t>256503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146356</t>
+          <t>147346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173146</t>
+          <t>174024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382965</t>
+          <t>382132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>426166</t>
+          <t>424938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64646</t>
+          <t>64434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99991</t>
+          <t>95748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>50053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78802</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123368</t>
+          <t>122456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166773</t>
+          <t>167168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318697</t>
+          <t>322940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354042</t>
+          <t>354254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222701</t>
+          <t>222944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251502</t>
+          <t>251450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553418</t>
+          <t>553023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596823</t>
+          <t>597735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300778</t>
+          <t>300958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>363978</t>
+          <t>365159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190384</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>244971</t>
+          <t>242807</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506992</t>
+          <t>506861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587553</t>
+          <t>591211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1054727</t>
+          <t>1053546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1117927</t>
+          <t>1117747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703745</t>
+          <t>705909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>758332</t>
+          <t>757957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1779868</t>
+          <t>1776210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1860429</t>
+          <t>1860560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44148</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69834</t>
+          <t>69751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39906</t>
+          <t>39719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68948</t>
+          <t>69005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101015</t>
+          <t>101075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171261</t>
+          <t>171344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196947</t>
+          <t>199068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126417</t>
+          <t>126604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>144510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306403</t>
+          <t>306343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>338470</t>
+          <t>338413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80470</t>
+          <t>78810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115963</t>
+          <t>113061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69255</t>
+          <t>69112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132093</t>
+          <t>131189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175926</t>
+          <t>174781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292377</t>
+          <t>295279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327870</t>
+          <t>329530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204516</t>
+          <t>204659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231330</t>
+          <t>229878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506185</t>
+          <t>507330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>550018</t>
+          <t>550922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92165</t>
+          <t>92818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128031</t>
+          <t>129291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79272</t>
+          <t>81305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152324</t>
+          <t>152958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200433</t>
+          <t>195174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233627</t>
+          <t>232367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269493</t>
+          <t>268840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>190344</t>
+          <t>188311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217636</t>
+          <t>216324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430841</t>
+          <t>436100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>478950</t>
+          <t>478316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105946</t>
+          <t>105597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82719</t>
+          <t>82942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134307</t>
+          <t>134553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293299</t>
+          <t>293648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326676</t>
+          <t>326686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239625</t>
+          <t>239402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>270170</t>
+          <t>271119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>543325</t>
+          <t>542540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>587282</t>
+          <t>587036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>318451</t>
+          <t>316701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384700</t>
+          <t>384864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191645</t>
+          <t>189877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525085</t>
+          <t>523190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>613144</t>
+          <t>606579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1025637</t>
+          <t>1025473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1091886</t>
+          <t>1093636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>786267</t>
+          <t>790028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>840409</t>
+          <t>842177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1829247</t>
+          <t>1835812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1917306</t>
+          <t>1919201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89090</t>
+          <t>87901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44184</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65995</t>
+          <t>66229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106092</t>
+          <t>107666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146449</t>
+          <t>147426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243146</t>
+          <t>244335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275690</t>
+          <t>276846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191902</t>
+          <t>191668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213713</t>
+          <t>213689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443684</t>
+          <t>442707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484041</t>
+          <t>482467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170744</t>
+          <t>173635</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83476</t>
+          <t>85815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114214</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93178</t>
+          <t>107780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275265</t>
+          <t>276286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630480</t>
+          <t>627589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>758275</t>
+          <t>751047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280403</t>
+          <t>280534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>308802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920576</t>
+          <t>919555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1102663</t>
+          <t>1088061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41510</t>
+          <t>42689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71472</t>
+          <t>72105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66064</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165148</t>
+          <t>165115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117009</t>
+          <t>116681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235031</t>
+          <t>237233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265788</t>
+          <t>265155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295750</t>
+          <t>294571</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150170</t>
+          <t>150203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249254</t>
+          <t>248483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>417547</t>
+          <t>415345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>535569</t>
+          <t>535897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82978</t>
+          <t>84236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122579</t>
+          <t>122528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64619</t>
+          <t>63140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128579</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160297</t>
+          <t>159833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239122</t>
+          <t>234171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347629</t>
+          <t>347680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>385972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348925</t>
+          <t>349901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412885</t>
+          <t>414364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>713541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>787415</t>
+          <t>787879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221407</t>
+          <t>221500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>403545</t>
+          <t>403377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>296499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>435034</t>
+          <t>430214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>547345</t>
+          <t>547157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>784691</t>
+          <t>791217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1537383</t>
+          <t>1537551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1719521</t>
+          <t>1719428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1010302</t>
+          <t>1015122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1143465</t>
+          <t>1148837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2601573</t>
+          <t>2595047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2838919</t>
+          <t>2839107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P68-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64651</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94876</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23011</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42974</t>
+          <t>42740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94512</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134657</t>
+          <t>133607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284273</t>
+          <t>281004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314498</t>
+          <t>314306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111673</t>
+          <t>111907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131636</t>
+          <t>131692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>399139</t>
+          <t>400189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>440437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125011</t>
+          <t>125571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169085</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40992</t>
+          <t>40374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67529</t>
+          <t>66087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172114</t>
+          <t>173584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223680</t>
+          <t>225160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>382360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426910</t>
+          <t>426350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198573</t>
+          <t>200015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225110</t>
+          <t>225728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>594343</t>
+          <t>592863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645909</t>
+          <t>644439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91825</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130773</t>
+          <t>129831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>59307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135314</t>
+          <t>134151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179633</t>
+          <t>181405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276647</t>
+          <t>277589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315595</t>
+          <t>317398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155168</t>
+          <t>153806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178137</t>
+          <t>178054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>440899</t>
+          <t>439127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>485218</t>
+          <t>486381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118109</t>
+          <t>116747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160618</t>
+          <t>159018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71770</t>
+          <t>72577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106432</t>
+          <t>103736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198277</t>
+          <t>198810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252820</t>
+          <t>250606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>394327</t>
+          <t>395927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>436836</t>
+          <t>438198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281170</t>
+          <t>283866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315832</t>
+          <t>315025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689727</t>
+          <t>691941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>744270</t>
+          <t>743737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>434510</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>510003</t>
+          <t>508849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>190991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247541</t>
+          <t>247029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>646055</t>
+          <t>648329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>740870</t>
+          <t>738299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1383432</t>
+          <t>1384586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1458925</t>
+          <t>1463337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>773923</t>
+          <t>774435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>825075</t>
+          <t>830473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2174029</t>
+          <t>2176600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2268844</t>
+          <t>2266570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64228</t>
+          <t>63556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93602</t>
+          <t>93736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94778</t>
+          <t>94753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131923</t>
+          <t>131267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175335</t>
+          <t>175201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204709</t>
+          <t>205381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112199</t>
+          <t>114203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135235</t>
+          <t>135662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>298289</t>
+          <t>298945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335434</t>
+          <t>335459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77025</t>
+          <t>77166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>111898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>80505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135994</t>
+          <t>134943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179462</t>
+          <t>181687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297659</t>
+          <t>296793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331666</t>
+          <t>331525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193002</t>
+          <t>191091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221583</t>
+          <t>221540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>500825</t>
+          <t>498600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>544293</t>
+          <t>545344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65886</t>
+          <t>64799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97227</t>
+          <t>96910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40318</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66996</t>
+          <t>67291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111793</t>
+          <t>112534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154599</t>
+          <t>156744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225162</t>
+          <t>225479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256503</t>
+          <t>257590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147346</t>
+          <t>147051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174024</t>
+          <t>173299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382132</t>
+          <t>379987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>424197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64434</t>
+          <t>67209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95748</t>
+          <t>97887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78559</t>
+          <t>79355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122456</t>
+          <t>123889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167168</t>
+          <t>169410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322940</t>
+          <t>320801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354254</t>
+          <t>351479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222944</t>
+          <t>222148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251450</t>
+          <t>250637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553023</t>
+          <t>550781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>597735</t>
+          <t>596302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300958</t>
+          <t>298880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365159</t>
+          <t>363016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242807</t>
+          <t>245637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506861</t>
+          <t>505548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>591211</t>
+          <t>585496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1053546</t>
+          <t>1055689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1117747</t>
+          <t>1119825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705909</t>
+          <t>703079</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>757957</t>
+          <t>758007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1776210</t>
+          <t>1781925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1860560</t>
+          <t>1861873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69751</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39719</t>
+          <t>39799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69005</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101075</t>
+          <t>100221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171344</t>
+          <t>171506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199068</t>
+          <t>198971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126604</t>
+          <t>126524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144510</t>
+          <t>145078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306343</t>
+          <t>307197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>338413</t>
+          <t>339762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78810</t>
+          <t>80785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113061</t>
+          <t>117457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69112</t>
+          <t>70931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131189</t>
+          <t>130929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174781</t>
+          <t>176681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295279</t>
+          <t>290883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>329530</t>
+          <t>327555</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204659</t>
+          <t>202840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229878</t>
+          <t>231304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>507330</t>
+          <t>505430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>550922</t>
+          <t>551182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>91172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129291</t>
+          <t>127444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81305</t>
+          <t>79081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152958</t>
+          <t>154833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195174</t>
+          <t>196432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232367</t>
+          <t>234214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268840</t>
+          <t>270486</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188311</t>
+          <t>190535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216324</t>
+          <t>218605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436100</t>
+          <t>434842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>478316</t>
+          <t>476441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72559</t>
+          <t>72435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105597</t>
+          <t>105055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51225</t>
+          <t>51869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>82325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134553</t>
+          <t>133009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>177951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293648</t>
+          <t>294190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326686</t>
+          <t>326810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239402</t>
+          <t>240019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271119</t>
+          <t>270475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>542540</t>
+          <t>543638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>587036</t>
+          <t>588580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>316701</t>
+          <t>315797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384864</t>
+          <t>384409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189877</t>
+          <t>191223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>523190</t>
+          <t>523285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>606579</t>
+          <t>608126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1025473</t>
+          <t>1025928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1093636</t>
+          <t>1094540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>790028</t>
+          <t>789909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>842177</t>
+          <t>840831</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1835812</t>
+          <t>1834265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1919201</t>
+          <t>1919106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71215</t>
+          <t>75044</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87901</t>
+          <t>92762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54681</t>
+          <t>59821</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>49776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66229</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>125897</t>
+          <t>134865</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107666</t>
+          <t>116000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147426</t>
+          <t>158184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>261021</t>
+          <t>290941</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244335</t>
+          <t>273223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276846</t>
+          <t>306513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>203216</t>
+          <t>219464</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191668</t>
+          <t>205663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213689</t>
+          <t>229509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>464236</t>
+          <t>510404</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442707</t>
+          <t>487085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482467</t>
+          <t>529269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332236</t>
+          <t>365985</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332236</t>
+          <t>365985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>332236</t>
+          <t>365985</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>257897</t>
+          <t>279285</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>257897</t>
+          <t>279285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>257897</t>
+          <t>279285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>590133</t>
+          <t>645269</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>590133</t>
+          <t>645269</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>590133</t>
+          <t>645269</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111983</t>
+          <t>132997</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50177</t>
+          <t>111006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173635</t>
+          <t>158980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98730</t>
+          <t>107455</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85815</t>
+          <t>93612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114083</t>
+          <t>124352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>210712</t>
+          <t>240452</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107780</t>
+          <t>211110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276286</t>
+          <t>269155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>689241</t>
+          <t>490744</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>627589</t>
+          <t>464761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>751047</t>
+          <t>512735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>295887</t>
+          <t>333169</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280534</t>
+          <t>316272</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308802</t>
+          <t>347012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>985129</t>
+          <t>823913</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919555</t>
+          <t>795210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1088061</t>
+          <t>853255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>801224</t>
+          <t>623741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>801224</t>
+          <t>623741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>801224</t>
+          <t>623741</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>394617</t>
+          <t>440624</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>394617</t>
+          <t>440624</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>394617</t>
+          <t>440624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1195841</t>
+          <t>1064365</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1195841</t>
+          <t>1064365</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1195841</t>
+          <t>1064365</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55277</t>
+          <t>68862</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42689</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72105</t>
+          <t>86538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96908</t>
+          <t>70712</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66835</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165115</t>
+          <t>84712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152184</t>
+          <t>139574</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116681</t>
+          <t>117837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237233</t>
+          <t>163762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281983</t>
+          <t>332149</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265155</t>
+          <t>314473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294571</t>
+          <t>349427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218410</t>
+          <t>258421</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150203</t>
+          <t>244421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248483</t>
+          <t>271126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>500394</t>
+          <t>590570</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>415345</t>
+          <t>566382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>535897</t>
+          <t>612307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>337260</t>
+          <t>401011</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>337260</t>
+          <t>401011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>337260</t>
+          <t>401011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>315318</t>
+          <t>329133</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>315318</t>
+          <t>329133</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>315318</t>
+          <t>329133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>652578</t>
+          <t>730144</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>652578</t>
+          <t>730144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>652578</t>
+          <t>730144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>101030</t>
+          <t>108107</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84236</t>
+          <t>89243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122528</t>
+          <t>129283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>103896</t>
+          <t>107345</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63140</t>
+          <t>92252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127603</t>
+          <t>123135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>204926</t>
+          <t>215452</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159833</t>
+          <t>192546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234171</t>
+          <t>242445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>369178</t>
+          <t>407825</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347680</t>
+          <t>386649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>385972</t>
+          <t>426689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>373608</t>
+          <t>337964</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349901</t>
+          <t>322174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414364</t>
+          <t>353057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>742786</t>
+          <t>745789</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713541</t>
+          <t>718796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>787879</t>
+          <t>768695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>470208</t>
+          <t>515932</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>470208</t>
+          <t>515932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>470208</t>
+          <t>515932</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>477504</t>
+          <t>445309</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>477504</t>
+          <t>445309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>477504</t>
+          <t>445309</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>947712</t>
+          <t>961241</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>947712</t>
+          <t>961241</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>947712</t>
+          <t>961241</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221500</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>403377</t>
+          <t>427477</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>354215</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296499</t>
+          <t>318644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430214</t>
+          <t>374504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>693720</t>
+          <t>730344</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>547157</t>
+          <t>680340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>791217</t>
+          <t>782010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1601423</t>
+          <t>1521659</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1537551</t>
+          <t>1479192</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1719428</t>
+          <t>1560676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1091121</t>
+          <t>1149017</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1015122</t>
+          <t>1119847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1148837</t>
+          <t>1175707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2692544</t>
+          <t>2670676</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2595047</t>
+          <t>2619010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2839107</t>
+          <t>2720680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P68-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
